--- a/forms/trg/Formulir_TRG_tnaq-rg.xlsx
+++ b/forms/trg/Formulir_TRG_tnaq-rg.xlsx
@@ -564,7 +564,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Formulir kelengkapan data: Transportation and Air Quality  Research Group</t>
+          <t>Formulir kelengkapan data: Transportation and Air Quality Research Group</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Anggota Transportation and Air Quality  Research Group</t>
+          <t>Anggota Transportation and Air Quality Research Group</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Profil Transportation and Air Quality  Research Group</t>
+          <t>Profil Transportation and Air Quality Research Group</t>
         </is>
       </c>
     </row>

--- a/forms/trg/Formulir_TRG_tnaq-rg.xlsx
+++ b/forms/trg/Formulir_TRG_tnaq-rg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B49)</f>
+        <f>COUNTA(Anggota!B5:B50)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F49)</f>
+        <f>COUNTA(Anggota!F5:F50)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Ir. Rasdiana Zakaria, S.T., M.T</t>
+          <t>Prof. Dr. Ir. Hj. Sumarni Hamid Aly, MT., IPU</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Environmental Risk Management</t>
+          <t>Transportation and Air Quality</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,17 +933,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-1534-8443</t>
+          <t>0000-0002-8328-1930</t>
         </is>
       </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6671275</t>
+          <t>21966</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57201774235</t>
+          <t>56720927100</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -962,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Ir. Nurul Masyiah Rani Harusi, ST., M.Eng</t>
+          <t>Ir. Rasdiana Zakaria, S.T., M.T</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -977,7 +973,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Air Pollution</t>
+          <t>Environmental Risk Management</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -986,17 +982,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-4479-9649</t>
+          <t>0000-0002-1534-8443</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>https://sinta.kemdikbud.go.id/authors/scopusanalysis/6783007</t>
+          <t>6671275</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57217107296</t>
+          <t>57201774235</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1011,12 +1007,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Eng. Muralia Hustim, ST., MT., IPM., AER</t>
+          <t>Ir. Nurul Masyiah Rani Harusi, ST., M.Eng</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1026,7 +1022,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Environmental Noise</t>
+          <t>Air Pollution</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1035,17 +1031,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-8323-1549</t>
+          <t>0000-0002-4479-9649</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>5977747</t>
+          <t>https://sinta.kemdikbud.go.id/authors/scopusanalysis/6783007</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>55438107000</t>
+          <t>57217107296</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1060,12 +1056,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Eng. Ir. Ibrahim Djamaluddin, ST., M.Eng</t>
+          <t>Dr. Eng. Muralia Hustim, ST., MT., IPM., AER</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1075,7 +1071,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Environmental Geotechnical</t>
+          <t>Environmental Noise</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1084,17 +1080,17 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-2963-1899</t>
+          <t>0000-0001-8323-1549</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6694217</t>
+          <t>5977747</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>24829377600</t>
+          <t>55438107000</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1109,12 +1105,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr.Eng. Ir. Muhammad Isran Ramli, ST., MT., IPM., AER</t>
+          <t>Dr. Eng. Ir. Ibrahim Djamaluddin, ST., M.Eng</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1124,7 +1120,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Transportation System Engineering Laboratory</t>
+          <t>Environmental Geotechnical</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1133,17 +1129,17 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5904-1358</t>
+          <t>0000-0002-2963-1899</t>
         </is>
       </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>5977376</t>
+          <t>6694217</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57194179510</t>
+          <t>24829377600</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1158,12 +1154,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Ir. Rasdiana Zakaria, S.T., M.T</t>
+          <t>Prof. Dr.Eng. Ir. Muhammad Isran Ramli, ST., MT., IPM., AER</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1173,7 +1169,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Environmental Risk Management</t>
+          <t>Transportation System Engineering Laboratory</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1182,17 +1178,17 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-1534-8443</t>
+          <t>0000-0001-5904-1358</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
         <is>
-          <t>6671275</t>
+          <t>5977376</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57201774235</t>
+          <t>57194179510</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1207,12 +1203,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Ir. Nurul Masyiah Rani Harusi, ST., M.Eng</t>
+          <t>Ir. Rasdiana Zakaria, S.T., M.T</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1222,7 +1218,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Air Pollution</t>
+          <t>Environmental Risk Management</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1231,17 +1227,17 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-4479-9649</t>
+          <t>0000-0002-1534-8443</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
         <is>
-          <t>https://sinta.kemdikbud.go.id/authors/scopusanalysis/6783007</t>
+          <t>6671275</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>57217107296</t>
+          <t>57201774235</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1256,12 +1252,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Eng. Muralia Hustim, ST., MT., IPM., AER</t>
+          <t>Ir. Nurul Masyiah Rani Harusi, ST., M.Eng</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1271,7 +1267,7 @@
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Environmental Noise</t>
+          <t>Air Pollution</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1280,17 +1276,17 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-8323-1549</t>
+          <t>0000-0002-4479-9649</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
         <is>
-          <t>5977747</t>
+          <t>https://sinta.kemdikbud.go.id/authors/scopusanalysis/6783007</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>55438107000</t>
+          <t>57217107296</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1305,12 +1301,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Eng. Ir. Ibrahim Djamaluddin, ST., M.Eng</t>
+          <t>Dr. Eng. Muralia Hustim, ST., MT., IPM., AER</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1320,7 +1316,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Environmental Geotechnical</t>
+          <t>Environmental Noise</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1329,17 +1325,17 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-2963-1899</t>
+          <t>0000-0001-8323-1549</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>6694217</t>
+          <t>5977747</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>24829377600</t>
+          <t>55438107000</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1354,12 +1350,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr.Eng. Ir. Muhammad Isran Ramli, ST., MT., IPM., AER</t>
+          <t>Dr. Eng. Ir. Ibrahim Djamaluddin, ST., M.Eng</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1369,7 +1365,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Transportation System Engineering Laboratory</t>
+          <t>Environmental Geotechnical</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1378,17 +1374,17 @@
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5904-1358</t>
+          <t>0000-0002-2963-1899</t>
         </is>
       </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
-          <t>5977376</t>
+          <t>6694217</t>
         </is>
       </c>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>57194179510</t>
+          <t>24829377600</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -1403,31 +1399,43 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Ir. Ts. Dr. Yuen Choon Wah</t>
+          <t>Prof. Dr.Eng. Ir. Muhammad Isran Ramli, ST., MT., IPM., AER</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>University Malaya</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Head of Centre for Transportation Research</t>
+          <t>Transportation System Engineering Laboratory</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-5904-1358</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
+        <is>
+          <t>5977376</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>57194179510</t>
+        </is>
+      </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1440,22 +1448,22 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Khaerul Amru, S.T., M.Sc</t>
+          <t>Ir. Ts. Dr. Yuen Choon Wah</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>University Malaya</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Air Pollution</t>
+          <t>Head of Centre for Transportation Research</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1477,22 +1485,22 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Putri Humaira Salsabila, S.T.</t>
+          <t>Khaerul Amru, S.T., M.Sc</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Students of 2025 Hasanuddin University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Remote Sensing, Air Quality, and Environmental Monitoring</t>
+          <t>Air Pollution</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1514,17 +1522,17 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>A. M. Yunus Furqan Ramdani R, S.Hut.</t>
+          <t>Putri Humaira Salsabila, S.T.</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Students of 2025 Hasanuddin University</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -1551,22 +1559,22 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>A. Azizah Nurul Dinanti, S.T.</t>
+          <t>A. M. Yunus Furqan Ramdani R, S.Hut.</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Students of 2025 Hasanuddin University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Remote Sensing and Environmental Monitoring</t>
+          <t>Remote Sensing, Air Quality, and Environmental Monitoring</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
@@ -1588,12 +1596,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Rizieq Akbar Mubarak, S.T.</t>
+          <t>A. Azizah Nurul Dinanti, S.T.</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1603,7 +1611,7 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Air Pollution</t>
+          <t>Remote Sensing and Environmental Monitoring</t>
         </is>
       </c>
       <c r="F20" s="12" t="n"/>
@@ -1625,22 +1633,22 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>Andi Indah Fitria Wahyuni Safaat, S.T</t>
+          <t>Muhammad Rizieq Akbar Mubarak, S.T.</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Researchers of 2026 Hasanuddin University</t>
+          <t>Students of 2025 Hasanuddin University</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Air Microplastics</t>
+          <t>Air Pollution</t>
         </is>
       </c>
       <c r="F21" s="12" t="n"/>
@@ -1662,18 +1670,22 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Dr. Fransiskus Xaverius Mangga, S.Kom., M.T.</t>
+          <t>Andi Indah Fitria Wahyuni Safaat, S.T</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Researchers of 2026 Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Transportation Facilities</t>
+          <t>Air Microplastics</t>
         </is>
       </c>
       <c r="F22" s="12" t="n"/>
@@ -1695,22 +1707,18 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Khalil Jibran, S.T</t>
+          <t>Dr. Fransiskus Xaverius Mangga, S.Kom., M.T.</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n"/>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>Remote Sensing, Air Quality, and Environmental Monitoring</t>
+          <t>Transportation Facilities</t>
         </is>
       </c>
       <c r="F23" s="12" t="n"/>
@@ -1732,18 +1740,22 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Afief, S.T.</t>
+          <t>Muhammad Khalil Jibran, S.T</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="n"/>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Driving Cycle of Vehicle</t>
+          <t>Remote Sensing, Air Quality, and Environmental Monitoring</t>
         </is>
       </c>
       <c r="F24" s="12" t="n"/>
@@ -1765,22 +1777,18 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Hengky Pala'langan, S.T</t>
+          <t>Muhammad Afief, S.T.</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>Students of 2025 Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Remote Sensing and Environmental Monitoring</t>
+          <t>Driving Cycle of Vehicle</t>
         </is>
       </c>
       <c r="F25" s="12" t="n"/>
@@ -1802,12 +1810,12 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Alisyah Ismi Zahra Mardan, S.T</t>
+          <t>Hengky Pala'langan, S.T</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -1839,12 +1847,12 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Aisyah Handayani, S.T</t>
+          <t>Alisyah Ismi Zahra Mardan, S.T</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -1854,7 +1862,7 @@
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Air Pollution</t>
+          <t>Remote Sensing and Environmental Monitoring</t>
         </is>
       </c>
       <c r="F27" s="12" t="n"/>
@@ -1876,12 +1884,12 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Raif Rafii, S.T</t>
+          <t>Aisyah Handayani, S.T</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
@@ -1913,22 +1921,22 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Aprilia Damayanthi Azizuddin, S.T</t>
+          <t>Muhammad Raif Rafii, S.T</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>Students of 2026 Hasanuddin University</t>
+          <t>Students of 2025 Hasanuddin University</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Truck Emission</t>
+          <t>Air Pollution</t>
         </is>
       </c>
       <c r="F29" s="12" t="n"/>
@@ -1950,12 +1958,12 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Rahmatul Ain, S.T</t>
+          <t>Aprilia Damayanthi Azizuddin, S.T</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
@@ -1965,7 +1973,7 @@
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>Light vehicle emissions</t>
+          <t>Truck Emission</t>
         </is>
       </c>
       <c r="F30" s="12" t="n"/>
@@ -1987,12 +1995,12 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Rahmat Syamsudaris, S.T</t>
+          <t>Rahmatul Ain, S.T</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
@@ -2002,7 +2010,7 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>Green Open Space and Romote sensing</t>
+          <t>Light vehicle emissions</t>
         </is>
       </c>
       <c r="F31" s="12" t="n"/>
@@ -2024,12 +2032,12 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Nurfadillah Repina Mansur, S.T</t>
+          <t>Rahmat Syamsudaris, S.T</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
@@ -2039,7 +2047,7 @@
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>Air Pollution</t>
+          <t>Green Open Space and Romote sensing</t>
         </is>
       </c>
       <c r="F32" s="12" t="n"/>
@@ -2061,12 +2069,12 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Debby Utami Pratiwi Bakri, S.S., S.T.</t>
+          <t>Nurfadillah Repina Mansur, S.T</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -2076,7 +2084,7 @@
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Truck Emissions</t>
+          <t>Air Pollution</t>
         </is>
       </c>
       <c r="F33" s="12" t="n"/>
@@ -2098,12 +2106,12 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Suci Nur Ashadiqa S.T</t>
+          <t>Debby Utami Pratiwi Bakri, S.S., S.T.</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
@@ -2113,7 +2121,7 @@
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>Air Microplastics</t>
+          <t>Truck Emissions</t>
         </is>
       </c>
       <c r="F34" s="12" t="n"/>
@@ -2135,12 +2143,12 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Andi Artika Maharani S.T</t>
+          <t>Suci Nur Ashadiqa S.T</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
@@ -2172,12 +2180,12 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Andi Raja Arpandi Manankasi S.T</t>
+          <t>Andi Artika Maharani S.T</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -2209,12 +2217,12 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Irma Mispa Liwan S.T</t>
+          <t>Andi Raja Arpandi Manankasi S.T</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -2244,10 +2252,26 @@
       <c r="A38" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="11" t="n"/>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Irma Mispa Liwan S.T</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Students of 2026 Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>Air Microplastics</t>
+        </is>
+      </c>
       <c r="F38" s="12" t="n"/>
       <c r="G38" s="12" t="n"/>
       <c r="H38" s="12" t="n"/>
@@ -2255,7 +2279,11 @@
       <c r="J38" s="12" t="n"/>
       <c r="K38" s="12" t="n"/>
       <c r="L38" s="12" t="n"/>
-      <c r="M38" s="12" t="n"/>
+      <c r="M38" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -2444,15 +2472,32 @@
       <c r="L49" s="12" t="n"/>
       <c r="M49" s="12" t="n"/>
     </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="12" t="n"/>
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="12" t="n"/>
+      <c r="E50" s="11" t="n"/>
+      <c r="F50" s="12" t="n"/>
+      <c r="G50" s="12" t="n"/>
+      <c r="H50" s="12" t="n"/>
+      <c r="I50" s="12" t="n"/>
+      <c r="J50" s="12" t="n"/>
+      <c r="K50" s="12" t="n"/>
+      <c r="L50" s="12" t="n"/>
+      <c r="M50" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
